--- a/resources/quality_schema_data_quality_fsl_template.xlsx
+++ b/resources/quality_schema_data_quality_fsl_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\iphRa\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC6B5FBE-B785-44FE-BF8D-9694F1355CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB56B479-A392-4D26-AE42-C6D4D1141482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="quality_schema_fsl" sheetId="1" r:id="rId1"/>
@@ -735,7 +735,7 @@
         <v>43</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" t="s">
         <v>14</v>
@@ -761,7 +761,7 @@
         <v>43</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F3" t="s">
         <v>15</v>
@@ -787,7 +787,7 @@
         <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
